--- a/testing/reports/excel/Security_Report.xlsx
+++ b/testing/reports/excel/Security_Report.xlsx
@@ -1312,7 +1312,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.01s</t>
+          <t>0.00s</t>
         </is>
       </c>
     </row>
